--- a/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_KEN_grids_kan10/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_KEN_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{52F1F6BA-A095-4189-B457-3EFDF8141139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FF0CD8C-4B7E-4F72-8DEE-D3EACE019EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -813,13 +813,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S03aH04,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S04aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S03aH03,S05aH08,S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S03aH02</t>
+    <t>S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S03aH03,S04aH02,S03aH02,S05aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08,S01aH03,S05aH02,S05aH03,S05aH06,S03aH04,S02aH02,S06aH06,S04aH03,S01aH06,S02aH03,S05aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S02aH09,S04aH09,S05aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S01aH02,S05aH10,S03aH01,S06aH09,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S01aH10,S03aH02,S05aH08,S01aH09,S04aH02</t>
+    <t>S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S04aH02,S04aH08,S06aH01,S01aH02,S05aH10,S01aH09,S01aH08,S02aH08,S06aH09,S05aH08,S02aH09,S04aH09,S05aH01,S03aH01,S02aH01,S02aH10,S05aH02,S01aH01,S04aH01,S06aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S02aH09,S04aH09,S05aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S01aH02,S05aH10,S03aH01,S06aH09,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01,S01aH10,S03aH02,S05aH08,S01aH09,S04aH02</v>
+        <v>S03aH09,S05aH09,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S01aH10,S03aH02,S04aH02,S04aH08,S06aH01,S01aH02,S05aH10,S01aH09,S01aH08,S02aH08,S06aH09,S05aH08,S02aH09,S04aH09,S05aH01,S03aH01,S02aH01,S02aH10,S05aH02,S01aH01,S04aH01,S06aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S03aH04,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S04aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S03aH03,S05aH08,S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S03aH02</v>
+        <v>S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH04,S02aH05,S06aH07,S03aH03,S04aH02,S03aH02,S05aH08,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S01aH02,S04aH04,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08,S01aH03,S05aH02,S05aH03,S05aH06,S03aH04,S02aH02,S06aH06,S04aH03,S01aH06,S02aH03,S05aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1542,7 +1542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C573C2E5-5BF7-4A92-8A99-DDE78552A302}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93A4E898-64F9-4917-B595-18494C56EFC4}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1686,7 +1686,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41D25B67-2339-4318-82CD-180A36259541}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F8E756C-31BD-4FDC-B22E-52EAAC26A4E7}">
   <dimension ref="B9:O1690"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -49028,7 +49028,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49EA8B97-A044-43EC-96FF-2B168495C2CC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A72CB86-4C65-4712-8F25-05D26D84DEEF}">
   <dimension ref="B9:IV71"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -74294,7 +74294,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9143C2-0E6B-485D-85F6-D3E5DA53F77A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAB91809-1A49-4DA6-9F3F-559BBAF19829}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -75164,7 +75164,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE4FC514-940C-4019-97B8-50E95A7D0F75}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4086960-FB66-4E53-A2EB-AB241F7F0247}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -76511,7 +76511,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD4CE9A-C65A-48D8-8CD1-94E59F002184}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF5DFE7D-741A-4B05-899E-3A2189DAD295}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -77198,7 +77198,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA8B6BA8-51C5-422B-A7EF-879A6ECAA747}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{972E1E2D-ADD8-446A-9A57-20A6D93EA7C2}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
